--- a/Ficha_Predial_IN_Piura_F-LA.xlsx
+++ b/Ficha_Predial_IN_Piura_F-LA.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATALOGO_V6" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_MAPA" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="CAT_COD">CATALOGO_V6!$A$8:$A$184</definedName>
@@ -68,7 +69,7 @@
     <definedName name="U_AP_6">LISTAS!$AT$4:$AT$32</definedName>
     <definedName name="U_ESP">LISTAS!$AU$4:$AU$180</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FICHA PREDIAL'!$A$1:$Y$161</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'INSTRUCCIONES'!$A$33:$E$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'INSTRUCCIONES'!$A$34:$E$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CATALOGO_V6'!$A$7:$I$184</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'CATALOGO_V6'!$7:$7</definedName>
   </definedNames>
@@ -861,7 +862,7 @@
     <col width="30" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>AUTORIDAD NACIONAL DE INFRAESTRUCTURA - ANIN</t>
@@ -891,7 +892,7 @@
       <c r="X1" s="2" t="n"/>
       <c r="Y1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>DIRECCIÓN DE INTERVENCIONES MULTISECTORIALES Y DE EMERGENCIA - DIME</t>
@@ -921,7 +922,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>SUBDIRECCIÓN DE ESTUDIOS DE INVERSIÓN</t>
@@ -952,7 +953,7 @@
       <c r="Y3" s="2" t="n"/>
     </row>
     <row r="4" ht="5" customHeight="1"/>
-    <row r="5">
+    <row r="5" ht="15" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>FICHA TÉCNICA PREDIAL</t>
@@ -991,7 +992,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
@@ -1020,14 +1021,14 @@
       <c r="X6" s="10" t="n"/>
       <c r="Y6" s="10" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Liberación de áreas · Equivalente a los formularios KoboToolbox F-LA-02 (ficha predial y socio-territorial) y F-LA-03 (inspección in situ y croquis)</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Proyecto IN Piura – CUI 2669244 · Coordenadas UTM WGS84 Zona 17S (EPSG:32717) · Versión FP-2026.10</t>
@@ -1099,7 +1100,7 @@
       <c r="X11" s="10" t="n"/>
       <c r="Y11" s="10" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="15" customHeight="1">
       <c r="B12" s="14" t="inlineStr">
         <is>
           <t>SOLICITANTE</t>
@@ -1133,7 +1134,7 @@
       <c r="X12" s="10" t="n"/>
       <c r="Y12" s="10" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="15" customHeight="1">
       <c r="B13" s="14" t="inlineStr">
         <is>
           <t>ASISTENTE PREDIAL</t>
@@ -1175,7 +1176,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="26" customHeight="1">
       <c r="B14" s="14" t="inlineStr">
         <is>
           <t>CÓDIGO DE LA UNIDAD (BLOQUE / LOTE SUS)</t>
@@ -1217,7 +1218,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="26" customHeight="1">
       <c r="B15" s="14" t="inlineStr">
         <is>
           <t>UBICACIÓN SEGÚN CATÁLOGO V6</t>
@@ -1257,7 +1258,7 @@
       <c r="X15" s="10" t="n"/>
       <c r="Y15" s="10" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="26" customHeight="1">
       <c r="B16" s="14" t="inlineStr">
         <is>
           <t>N° DE PREDIO EN LA UNIDAD</t>
@@ -1299,7 +1300,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1">
       <c r="B17" s="14" t="inlineStr">
         <is>
           <t>FECHA DE INSPECCIÓN</t>
@@ -1338,7 +1339,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="37" customHeight="1">
       <c r="B18" s="14" t="inlineStr">
         <is>
           <t>CONSENTIMIENTO USO DE DATOS PERSONALES (LEY 29733)</t>
@@ -1411,7 +1412,7 @@
       <c r="X20" s="7" t="n"/>
       <c r="Y20" s="7" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="26" customHeight="1">
       <c r="B21" s="14" t="inlineStr">
         <is>
           <t>SITUACIÓN REGISTRAL</t>
@@ -1450,7 +1451,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="26" customHeight="1">
       <c r="B22" s="14" t="inlineStr">
         <is>
           <t>TIPO DE PERSONERÍA (TITULAR REGISTRAL)</t>
@@ -1484,7 +1485,7 @@
       <c r="X22" s="5" t="n"/>
       <c r="Y22" s="5" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="26" customHeight="1">
       <c r="B23" s="14" t="inlineStr">
         <is>
           <t>TITULAR REGISTRAL (NOMBRE / RAZÓN SOCIAL)</t>
@@ -1514,7 +1515,7 @@
       <c r="X23" s="5" t="n"/>
       <c r="Y23" s="5" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="26" customHeight="1">
       <c r="B24" s="14" t="inlineStr">
         <is>
           <t>DOCUMENTOS EXHIBIDOS (hasta 3)</t>
@@ -1580,7 +1581,7 @@
       <c r="X26" s="7" t="n"/>
       <c r="Y26" s="7" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="26" customHeight="1">
       <c r="B27" s="14" t="inlineStr">
         <is>
           <t>CONDICIÓN JURÍDICA DEL PREDIANTE</t>
@@ -1619,7 +1620,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="26" customHeight="1">
       <c r="B28" s="14" t="inlineStr">
         <is>
           <t>ESTADO DE LA SUCESIÓN (si aplica)</t>
@@ -1661,7 +1662,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15" customHeight="1">
       <c r="B29" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">   2.1 PERSONA NATURAL (privado, posesionario, ocupante, sucesión)</t>
@@ -1691,7 +1692,7 @@
       <c r="X29" s="27" t="n"/>
       <c r="Y29" s="27" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15" customHeight="1">
       <c r="B30" s="14" t="inlineStr">
         <is>
           <t>NOMBRES</t>
@@ -1730,7 +1731,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15" customHeight="1">
       <c r="B31" s="14" t="inlineStr">
         <is>
           <t>DNI</t>
@@ -1769,7 +1770,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="26" customHeight="1">
       <c r="B32" s="14" t="inlineStr">
         <is>
           <t>ESTADO CIVIL</t>
@@ -1808,7 +1809,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15" customHeight="1">
       <c r="B33" s="14" t="inlineStr">
         <is>
           <t>CÓNYUGE / CONVIVIENTE</t>
@@ -1847,7 +1848,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15" customHeight="1">
       <c r="B34" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">   2.2 PERSONA JURÍDICA (comunidad campesina, entidad estatal, empresa o asociación)</t>
@@ -1877,7 +1878,7 @@
       <c r="X34" s="27" t="n"/>
       <c r="Y34" s="27" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="26" customHeight="1">
       <c r="B35" s="14" t="inlineStr">
         <is>
           <t>COMUNIDAD / ENTIDAD / RAZÓN SOCIAL</t>
@@ -1912,7 +1913,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="26" customHeight="1">
       <c r="B36" s="14" t="inlineStr">
         <is>
           <t>RUC</t>
@@ -1951,7 +1952,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="26" customHeight="1">
       <c r="B37" s="14" t="inlineStr">
         <is>
           <t>REPRESENTANTE / PRESIDENTE COMUNAL</t>
@@ -1990,7 +1991,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="26" customHeight="1">
       <c r="B38" s="14" t="inlineStr">
         <is>
           <t>DNI DEL REPRESENTANTE</t>
@@ -2029,7 +2030,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15" customHeight="1">
       <c r="B39" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">   2.3 DOMICILIO DEL PREDIANTE</t>
@@ -2059,7 +2060,7 @@
       <c r="X39" s="27" t="n"/>
       <c r="Y39" s="27" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15" customHeight="1">
       <c r="B40" s="29" t="inlineStr">
         <is>
           <t>DIRECCIÓN</t>
@@ -2158,7 +2159,7 @@
       <c r="X43" s="7" t="n"/>
       <c r="Y43" s="7" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15" customHeight="1">
       <c r="B44" s="14" t="inlineStr">
         <is>
           <t>NOMBRE DEL PREDIO</t>
@@ -2193,7 +2194,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="26" customHeight="1">
       <c r="B45" s="14" t="inlineStr">
         <is>
           <t>CENTRO POBLADO / SECTOR</t>
@@ -2257,7 +2258,7 @@
       <c r="X46" s="5" t="n"/>
       <c r="Y46" s="5" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="26" customHeight="1">
       <c r="B47" s="14" t="inlineStr">
         <is>
           <t>TIPO DE ACCESO</t>
@@ -2291,7 +2292,7 @@
       <c r="X47" s="5" t="n"/>
       <c r="Y47" s="5" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15" customHeight="1">
       <c r="B48" s="14" t="inlineStr">
         <is>
           <t>SISTEMA DE COORDENADAS</t>
@@ -2325,7 +2326,7 @@
       <c r="X48" s="10" t="n"/>
       <c r="Y48" s="10" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15" customHeight="1">
       <c r="B49" s="14" t="inlineStr">
         <is>
           <t>ESTE UTM (m)</t>
@@ -2364,7 +2365,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15" customHeight="1">
       <c r="B50" s="14" t="inlineStr">
         <is>
           <t>ALTITUD (m s.n.m.)</t>
@@ -2403,7 +2404,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15" customHeight="1">
       <c r="B51" s="14" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
@@ -2441,7 +2442,7 @@
       <c r="X51" s="18" t="n"/>
       <c r="Y51" s="18" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="26" customHeight="1">
       <c r="B52" s="14" t="inlineStr">
         <is>
           <t>DISTRITO</t>
@@ -2509,7 +2510,7 @@
       <c r="X54" s="7" t="n"/>
       <c r="Y54" s="7" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="26" customHeight="1">
       <c r="B55" s="14" t="inlineStr">
         <is>
           <t>USO ACTUAL DEL SUELO</t>
@@ -2548,7 +2549,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15" customHeight="1">
       <c r="B56" s="14" t="inlineStr">
         <is>
           <t>OCUPACIÓN OBSERVADA</t>
@@ -2587,7 +2588,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="26" customHeight="1">
       <c r="B57" s="14" t="inlineStr">
         <is>
           <t>EDIFICACIONES / CULTIVOS</t>
@@ -2621,7 +2622,7 @@
       <c r="X57" s="5" t="n"/>
       <c r="Y57" s="5" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15" customHeight="1">
       <c r="B58" s="14" t="inlineStr">
         <is>
           <t>TOPOGRAFÍA / PENDIENTE</t>
@@ -2655,7 +2656,7 @@
       <c r="X58" s="18" t="n"/>
       <c r="Y58" s="18" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="26" customHeight="1">
       <c r="B59" s="14" t="inlineStr">
         <is>
           <t>ESTADO DE LA COBERTURA VEGETAL</t>
@@ -2724,7 +2725,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15" customHeight="1">
       <c r="B61" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">   4.1 DATOS TÉCNICOS</t>
@@ -2754,7 +2755,7 @@
       <c r="X61" s="27" t="n"/>
       <c r="Y61" s="27" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="26" customHeight="1">
       <c r="B62" s="14" t="inlineStr">
         <is>
           <t>TIPO DE PREDIO</t>
@@ -2793,7 +2794,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="26" customHeight="1">
       <c r="B63" s="14" t="inlineStr">
         <is>
           <t>PERÍMETRO (m)</t>
@@ -2830,7 +2831,7 @@
       <c r="X63" s="10" t="n"/>
       <c r="Y63" s="10" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15" customHeight="1">
       <c r="B64" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">   4.2 COLINDANCIAS</t>
@@ -2860,7 +2861,7 @@
       <c r="X64" s="27" t="n"/>
       <c r="Y64" s="27" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15" customHeight="1">
       <c r="B65" s="29" t="inlineStr">
         <is>
           <t>LÍMITE</t>
@@ -3084,7 +3085,7 @@
       <c r="X72" s="7" t="n"/>
       <c r="Y72" s="7" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15" customHeight="1">
       <c r="B73" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">   5.1 DATOS TÉCNICOS</t>
@@ -3114,7 +3115,7 @@
       <c r="X73" s="27" t="n"/>
       <c r="Y73" s="27" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="26" customHeight="1">
       <c r="B74" s="14" t="inlineStr">
         <is>
           <t>ÁREA DEL PREDIO DENTRO DE LA UNIDAD (ha)</t>
@@ -3156,7 +3157,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15" customHeight="1">
       <c r="B75" s="14" t="inlineStr">
         <is>
           <t>% DEL PREDIO MATRIZ</t>
@@ -3196,7 +3197,7 @@
       <c r="X75" s="10" t="n"/>
       <c r="Y75" s="10" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15" customHeight="1">
       <c r="B76" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">   5.2 CARACTERÍSTICAS</t>
@@ -3226,7 +3227,7 @@
       <c r="X76" s="27" t="n"/>
       <c r="Y76" s="27" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="26" customHeight="1">
       <c r="B77" s="14" t="inlineStr">
         <is>
           <t>INTERFERENCIAS (hasta 3)</t>
@@ -3326,7 +3327,7 @@
       <c r="X79" s="18" t="n"/>
       <c r="Y79" s="18" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15" customHeight="1">
       <c r="B80" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">   5.3 DESCRIPCIÓN DE AFECTACIONES (obras y bienes existentes en el área)</t>
@@ -3595,7 +3596,7 @@
       <c r="X88" s="7" t="n"/>
       <c r="Y88" s="7" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" ht="26" customHeight="1">
       <c r="B89" s="14" t="inlineStr">
         <is>
           <t>ACEPTACIÓN DEL TITULAR / PREDIANTE</t>
@@ -3634,7 +3635,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="15" customHeight="1">
       <c r="B90" s="14" t="inlineStr">
         <is>
           <t>CONCLUSIÓN DE CAMPO</t>
@@ -3673,7 +3674,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="26" customHeight="1">
       <c r="B91" s="14" t="inlineStr">
         <is>
           <t>ACTA PREVISTA</t>
@@ -3773,7 +3774,7 @@
       <c r="X94" s="7" t="n"/>
       <c r="Y94" s="7" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15" customHeight="1">
       <c r="B95" s="38" t="inlineStr">
         <is>
           <t>Croquis: indicar el norte, linderos, colindantes, accesos, vértices numerados e interferencias.</t>
@@ -3803,7 +3804,7 @@
       <c r="X95" s="5" t="n"/>
       <c r="Y95" s="5" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15" customHeight="1">
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="5" t="n"/>
       <c r="D96" s="5" t="n"/>
@@ -3829,7 +3830,7 @@
       <c r="X96" s="5" t="n"/>
       <c r="Y96" s="5" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15" customHeight="1">
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="5" t="n"/>
       <c r="D97" s="5" t="n"/>
@@ -3855,7 +3856,7 @@
       <c r="X97" s="5" t="n"/>
       <c r="Y97" s="5" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15" customHeight="1">
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="5" t="n"/>
       <c r="D98" s="5" t="n"/>
@@ -3881,7 +3882,7 @@
       <c r="X98" s="5" t="n"/>
       <c r="Y98" s="5" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15" customHeight="1">
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="5" t="n"/>
       <c r="D99" s="5" t="n"/>
@@ -3907,7 +3908,7 @@
       <c r="X99" s="5" t="n"/>
       <c r="Y99" s="5" t="n"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15" customHeight="1">
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="5" t="n"/>
@@ -3933,7 +3934,7 @@
       <c r="X100" s="5" t="n"/>
       <c r="Y100" s="5" t="n"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15" customHeight="1">
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="5" t="n"/>
       <c r="D101" s="5" t="n"/>
@@ -3959,7 +3960,7 @@
       <c r="X101" s="5" t="n"/>
       <c r="Y101" s="5" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15" customHeight="1">
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="5" t="n"/>
       <c r="D102" s="5" t="n"/>
@@ -3985,7 +3986,7 @@
       <c r="X102" s="5" t="n"/>
       <c r="Y102" s="5" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15" customHeight="1">
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="5" t="n"/>
       <c r="D103" s="5" t="n"/>
@@ -4011,7 +4012,7 @@
       <c r="X103" s="5" t="n"/>
       <c r="Y103" s="5" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15" customHeight="1">
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="5" t="n"/>
       <c r="D104" s="5" t="n"/>
@@ -4037,7 +4038,7 @@
       <c r="X104" s="5" t="n"/>
       <c r="Y104" s="5" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15" customHeight="1">
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="5" t="n"/>
       <c r="D105" s="5" t="n"/>
@@ -4063,7 +4064,7 @@
       <c r="X105" s="5" t="n"/>
       <c r="Y105" s="5" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15" customHeight="1">
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="5" t="n"/>
       <c r="D106" s="5" t="n"/>
@@ -4089,7 +4090,7 @@
       <c r="X106" s="5" t="n"/>
       <c r="Y106" s="5" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15" customHeight="1">
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="5" t="n"/>
       <c r="D107" s="5" t="n"/>
@@ -4115,7 +4116,7 @@
       <c r="X107" s="5" t="n"/>
       <c r="Y107" s="5" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15" customHeight="1">
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="5" t="n"/>
       <c r="D108" s="5" t="n"/>
@@ -4141,7 +4142,7 @@
       <c r="X108" s="5" t="n"/>
       <c r="Y108" s="5" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15" customHeight="1">
       <c r="B109" s="29" t="inlineStr">
         <is>
           <t>N°</t>
@@ -4191,7 +4192,7 @@
       <c r="X109" s="15" t="n"/>
       <c r="Y109" s="15" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15" customHeight="1">
       <c r="B110" s="37" t="n">
         <v>1</v>
       </c>
@@ -4224,7 +4225,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="15" customHeight="1">
       <c r="B111" s="37" t="n">
         <v>2</v>
       </c>
@@ -4252,7 +4253,7 @@
       <c r="X111" s="5" t="n"/>
       <c r="Y111" s="5" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15" customHeight="1">
       <c r="B112" s="37" t="n">
         <v>3</v>
       </c>
@@ -4280,7 +4281,7 @@
       <c r="X112" s="5" t="n"/>
       <c r="Y112" s="5" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15" customHeight="1">
       <c r="B113" s="37" t="n">
         <v>4</v>
       </c>
@@ -4308,7 +4309,7 @@
       <c r="X113" s="5" t="n"/>
       <c r="Y113" s="5" t="n"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15" customHeight="1">
       <c r="B114" s="37" t="n">
         <v>5</v>
       </c>
@@ -4336,7 +4337,7 @@
       <c r="X114" s="5" t="n"/>
       <c r="Y114" s="5" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15" customHeight="1">
       <c r="B115" s="37" t="n">
         <v>6</v>
       </c>
@@ -4364,7 +4365,7 @@
       <c r="X115" s="5" t="n"/>
       <c r="Y115" s="5" t="n"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15" customHeight="1">
       <c r="B116" s="37" t="n">
         <v>7</v>
       </c>
@@ -4392,7 +4393,7 @@
       <c r="X116" s="5" t="n"/>
       <c r="Y116" s="5" t="n"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15" customHeight="1">
       <c r="B117" s="37" t="n">
         <v>8</v>
       </c>
@@ -4451,7 +4452,7 @@
       <c r="X119" s="7" t="n"/>
       <c r="Y119" s="7" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15" customHeight="1">
       <c r="B120" s="39" t="inlineStr">
         <is>
           <t>Insertar fotografía</t>
@@ -4485,7 +4486,7 @@
       <c r="X120" s="5" t="n"/>
       <c r="Y120" s="5" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15" customHeight="1">
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="5" t="n"/>
       <c r="D121" s="5" t="n"/>
@@ -4511,7 +4512,7 @@
       <c r="X121" s="5" t="n"/>
       <c r="Y121" s="5" t="n"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15" customHeight="1">
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="5" t="n"/>
       <c r="D122" s="5" t="n"/>
@@ -4537,7 +4538,7 @@
       <c r="X122" s="5" t="n"/>
       <c r="Y122" s="5" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15" customHeight="1">
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="5" t="n"/>
       <c r="D123" s="5" t="n"/>
@@ -4563,7 +4564,7 @@
       <c r="X123" s="5" t="n"/>
       <c r="Y123" s="5" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15" customHeight="1">
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="5" t="n"/>
       <c r="D124" s="5" t="n"/>
@@ -4589,7 +4590,7 @@
       <c r="X124" s="5" t="n"/>
       <c r="Y124" s="5" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15" customHeight="1">
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="5" t="n"/>
       <c r="D125" s="5" t="n"/>
@@ -4615,7 +4616,7 @@
       <c r="X125" s="5" t="n"/>
       <c r="Y125" s="5" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15" customHeight="1">
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="5" t="n"/>
       <c r="D126" s="5" t="n"/>
@@ -4641,7 +4642,7 @@
       <c r="X126" s="5" t="n"/>
       <c r="Y126" s="5" t="n"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15" customHeight="1">
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="5" t="n"/>
       <c r="D127" s="5" t="n"/>
@@ -4667,7 +4668,7 @@
       <c r="X127" s="5" t="n"/>
       <c r="Y127" s="5" t="n"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15" customHeight="1">
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="5" t="n"/>
       <c r="D128" s="5" t="n"/>
@@ -4693,7 +4694,7 @@
       <c r="X128" s="5" t="n"/>
       <c r="Y128" s="5" t="n"/>
     </row>
-    <row r="129">
+    <row r="129" ht="15" customHeight="1">
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="5" t="n"/>
       <c r="D129" s="5" t="n"/>
@@ -4719,7 +4720,7 @@
       <c r="X129" s="5" t="n"/>
       <c r="Y129" s="5" t="n"/>
     </row>
-    <row r="130">
+    <row r="130" ht="15" customHeight="1">
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="5" t="n"/>
       <c r="D130" s="5" t="n"/>
@@ -4745,7 +4746,7 @@
       <c r="X130" s="5" t="n"/>
       <c r="Y130" s="5" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15" customHeight="1">
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="5" t="n"/>
       <c r="D131" s="5" t="n"/>
@@ -4771,7 +4772,7 @@
       <c r="X131" s="5" t="n"/>
       <c r="Y131" s="5" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15" customHeight="1">
       <c r="B132" s="37" t="inlineStr">
         <is>
           <t>Foto 1 – Vista general del predio</t>
@@ -4810,7 +4811,7 @@
         </is>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="15" customHeight="1">
       <c r="B133" s="40" t="inlineStr">
         <is>
           <t>Archivo / N°:</t>
@@ -4850,7 +4851,7 @@
       </c>
     </row>
     <row r="134" ht="6" customHeight="1"/>
-    <row r="135">
+    <row r="135" ht="15" customHeight="1">
       <c r="B135" s="39" t="inlineStr">
         <is>
           <t>Insertar fotografía</t>
@@ -4884,7 +4885,7 @@
       <c r="X135" s="5" t="n"/>
       <c r="Y135" s="5" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15" customHeight="1">
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="5" t="n"/>
       <c r="D136" s="5" t="n"/>
@@ -4910,7 +4911,7 @@
       <c r="X136" s="5" t="n"/>
       <c r="Y136" s="5" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15" customHeight="1">
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="5" t="n"/>
       <c r="D137" s="5" t="n"/>
@@ -4936,7 +4937,7 @@
       <c r="X137" s="5" t="n"/>
       <c r="Y137" s="5" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15" customHeight="1">
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="5" t="n"/>
       <c r="D138" s="5" t="n"/>
@@ -4962,7 +4963,7 @@
       <c r="X138" s="5" t="n"/>
       <c r="Y138" s="5" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15" customHeight="1">
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="5" t="n"/>
       <c r="D139" s="5" t="n"/>
@@ -4988,7 +4989,7 @@
       <c r="X139" s="5" t="n"/>
       <c r="Y139" s="5" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15" customHeight="1">
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="5" t="n"/>
       <c r="D140" s="5" t="n"/>
@@ -5014,7 +5015,7 @@
       <c r="X140" s="5" t="n"/>
       <c r="Y140" s="5" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15" customHeight="1">
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="5" t="n"/>
       <c r="D141" s="5" t="n"/>
@@ -5040,7 +5041,7 @@
       <c r="X141" s="5" t="n"/>
       <c r="Y141" s="5" t="n"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15" customHeight="1">
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="5" t="n"/>
       <c r="D142" s="5" t="n"/>
@@ -5066,7 +5067,7 @@
       <c r="X142" s="5" t="n"/>
       <c r="Y142" s="5" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15" customHeight="1">
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="5" t="n"/>
       <c r="D143" s="5" t="n"/>
@@ -5092,7 +5093,7 @@
       <c r="X143" s="5" t="n"/>
       <c r="Y143" s="5" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15" customHeight="1">
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="5" t="n"/>
       <c r="D144" s="5" t="n"/>
@@ -5118,7 +5119,7 @@
       <c r="X144" s="5" t="n"/>
       <c r="Y144" s="5" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15" customHeight="1">
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="5" t="n"/>
       <c r="D145" s="5" t="n"/>
@@ -5144,7 +5145,7 @@
       <c r="X145" s="5" t="n"/>
       <c r="Y145" s="5" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" ht="15" customHeight="1">
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="5" t="n"/>
       <c r="D146" s="5" t="n"/>
@@ -5170,7 +5171,7 @@
       <c r="X146" s="5" t="n"/>
       <c r="Y146" s="5" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15" customHeight="1">
       <c r="B147" s="37" t="inlineStr">
         <is>
           <t>Foto 3 – Linderos, hitos o accesos</t>
@@ -5209,7 +5210,7 @@
         </is>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="15" customHeight="1">
       <c r="B148" s="40" t="inlineStr">
         <is>
           <t>Archivo / N°:</t>
@@ -5315,7 +5316,7 @@
       <c r="X151" s="15" t="n"/>
       <c r="Y151" s="15" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15" customHeight="1">
       <c r="B152" s="42" t="n"/>
       <c r="C152" s="5" t="n"/>
       <c r="D152" s="5" t="n"/>
@@ -5339,7 +5340,7 @@
       <c r="X152" s="5" t="n"/>
       <c r="Y152" s="5" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15" customHeight="1">
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="5" t="n"/>
       <c r="D153" s="5" t="n"/>
@@ -5363,7 +5364,7 @@
       <c r="X153" s="5" t="n"/>
       <c r="Y153" s="5" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15" customHeight="1">
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="5" t="n"/>
       <c r="D154" s="5" t="n"/>
@@ -5387,7 +5388,7 @@
       <c r="X154" s="5" t="n"/>
       <c r="Y154" s="5" t="n"/>
     </row>
-    <row r="155">
+    <row r="155" ht="15" customHeight="1">
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="5" t="n"/>
       <c r="D155" s="5" t="n"/>
@@ -5411,7 +5412,7 @@
       <c r="X155" s="5" t="n"/>
       <c r="Y155" s="5" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15" customHeight="1">
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="5" t="n"/>
       <c r="D156" s="5" t="n"/>
@@ -5435,7 +5436,7 @@
       <c r="X156" s="5" t="n"/>
       <c r="Y156" s="5" t="n"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15" customHeight="1">
       <c r="B157" s="43">
         <f>IF(G30&lt;&gt;"",G30&amp;" "&amp;S30,IF(G35&lt;&gt;"",G35,"Nombre:"))</f>
         <v/>
@@ -5469,7 +5470,7 @@
       <c r="X157" s="5" t="n"/>
       <c r="Y157" s="5" t="n"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15" customHeight="1">
       <c r="B158" s="44" t="inlineStr">
         <is>
           <t>Huella digital (si no firma)</t>
@@ -5505,7 +5506,7 @@
       <c r="Y158" s="5" t="n"/>
     </row>
     <row r="159" ht="6" customHeight="1"/>
-    <row r="160">
+    <row r="160" ht="15" customHeight="1">
       <c r="B160" s="14" t="inlineStr">
         <is>
           <t>FECHA DE ELABORACIÓN</t>
@@ -6148,7 +6149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6242,2850 +6243,2858 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="49" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t>9. Sincronización con el aplicativo: una vez llenada, importe esta ficha en Liberación de Áreas › «2 · Plantillas Excel / Kobo» › Ficha técnica predial completa. Entra como F-LA-02 + F-LA-03, igual que un envío del formulario Kobo «FP – Ficha técnica predial completa». No cambie el nombre de las hojas ni borre la hoja oculta _MAPA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>LEYENDA DE CELDAS</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr"/>
-      <c r="B16" s="50" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr"/>
+      <c r="B17" s="50" t="inlineStr">
         <is>
           <t>Etiqueta del dato</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="51" t="inlineStr"/>
-      <c r="B17" s="50" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="51" t="inlineStr"/>
+      <c r="B18" s="50" t="inlineStr">
         <is>
           <t>Entrada libre (texto, número, fecha)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr"/>
-      <c r="B18" s="50" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr"/>
+      <c r="B19" s="50" t="inlineStr">
         <is>
           <t>Lista desplegable (elija un valor)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr"/>
-      <c r="B19" s="50" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr"/>
+      <c r="B20" s="50" t="inlineStr">
         <is>
           <t>Automático (fórmula, no editar)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="49" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="49" t="inlineStr">
         <is>
           <t>ASISTENTES PREDIALES (catálogo V6)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="52" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="52" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B22" s="52" t="inlineStr">
+      <c r="B23" s="52" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C22" s="52" t="inlineStr">
+      <c r="C23" s="52" t="inlineStr">
         <is>
           <t>Unidades asignadas</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="53" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="53" t="inlineStr">
         <is>
           <t>AP-1</t>
         </is>
       </c>
-      <c r="B23" s="53" t="inlineStr">
+      <c r="B24" s="53" t="inlineStr">
         <is>
           <t>Diusberto Peña López</t>
         </is>
       </c>
-      <c r="C23" s="53">
+      <c r="C24" s="53">
         <f>COUNTIF(CAT_ASIS,"AP-1")</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="53" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="53" t="inlineStr">
         <is>
           <t>AP-2</t>
         </is>
       </c>
-      <c r="B24" s="53" t="inlineStr">
+      <c r="B25" s="53" t="inlineStr">
         <is>
           <t>Didier Lucrecio Salvador García</t>
         </is>
       </c>
-      <c r="C24" s="53">
+      <c r="C25" s="53">
         <f>COUNTIF(CAT_ASIS,"AP-2")</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="53" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="53" t="inlineStr">
         <is>
           <t>AP-3</t>
         </is>
       </c>
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B26" s="53" t="inlineStr">
         <is>
           <t>Miguel Ángel López Maza</t>
         </is>
       </c>
-      <c r="C25" s="53">
+      <c r="C26" s="53">
         <f>COUNTIF(CAT_ASIS,"AP-3")</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="53" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="53" t="inlineStr">
         <is>
           <t>AP-4</t>
         </is>
       </c>
-      <c r="B26" s="53" t="inlineStr">
+      <c r="B27" s="53" t="inlineStr">
         <is>
           <t>Walter Córdova Córdova</t>
         </is>
       </c>
-      <c r="C26" s="53">
+      <c r="C27" s="53">
         <f>COUNTIF(CAT_ASIS,"AP-4")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="53" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="53" t="inlineStr">
         <is>
           <t>AP-5</t>
         </is>
       </c>
-      <c r="B27" s="53" t="inlineStr">
+      <c r="B28" s="53" t="inlineStr">
         <is>
           <t>Eli Moisés Tocto Padilla</t>
         </is>
       </c>
-      <c r="C27" s="53">
+      <c r="C28" s="53">
         <f>COUNTIF(CAT_ASIS,"AP-5")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="53" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="53" t="inlineStr">
         <is>
           <t>AP-6</t>
         </is>
       </c>
-      <c r="B28" s="53" t="inlineStr">
+      <c r="B29" s="53" t="inlineStr">
         <is>
           <t>Rubén García García</t>
         </is>
       </c>
-      <c r="C28" s="53">
+      <c r="C29" s="53">
         <f>COUNTIF(CAT_ASIS,"AP-6")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="53" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t>ESP</t>
         </is>
       </c>
-      <c r="B29" s="53" t="inlineStr">
+      <c r="B30" s="53" t="inlineStr">
         <is>
           <t>Especialista (ESP)</t>
         </is>
       </c>
-      <c r="C29" s="53">
+      <c r="C30" s="53">
         <f>COUNTA(CAT_COD)</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="54" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="54" t="inlineStr">
         <is>
           <t>Por asignar (sin asistente; disponibles para ESP)</t>
         </is>
       </c>
-      <c r="C30" s="54">
+      <c r="C31" s="54">
         <f>COUNTIF(CAT_ASIS,"PENDIENTE")</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="49" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr">
         <is>
           <t>CORRESPONDENCIA FICHA ↔ KOBOTOOLBOX (F-LA-02 / F-LA-03)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="52" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="52" t="inlineStr">
         <is>
           <t>Sección</t>
         </is>
       </c>
-      <c r="B33" s="52" t="inlineStr">
+      <c r="B34" s="52" t="inlineStr">
         <is>
           <t>Dato de la ficha</t>
         </is>
       </c>
-      <c r="C33" s="52" t="inlineStr">
+      <c r="C34" s="52" t="inlineStr">
         <is>
           <t>Celda</t>
         </is>
       </c>
-      <c r="D33" s="52" t="inlineStr">
+      <c r="D34" s="52" t="inlineStr">
         <is>
           <t>Campo Kobo (XLSForm)</t>
         </is>
       </c>
-      <c r="E33" s="52" t="inlineStr">
+      <c r="E34" s="52" t="inlineStr">
         <is>
           <t>Tipo de entrada</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="55" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B34" s="55" t="inlineStr">
+      <c r="B35" s="55" t="inlineStr">
         <is>
           <t>PROYECTO</t>
         </is>
       </c>
-      <c r="C34" s="55" t="inlineStr">
+      <c r="C35" s="55" t="inlineStr">
         <is>
           <t>G11</t>
         </is>
       </c>
-      <c r="D34" s="55" t="inlineStr">
+      <c r="D35" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E34" s="55" t="inlineStr">
+      <c r="E35" s="55" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="56" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="56" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B35" s="56" t="inlineStr">
+      <c r="B36" s="56" t="inlineStr">
         <is>
           <t>SOLICITANTE</t>
         </is>
       </c>
-      <c r="C35" s="56" t="inlineStr">
+      <c r="C36" s="56" t="inlineStr">
         <is>
           <t>G12</t>
         </is>
       </c>
-      <c r="D35" s="56" t="inlineStr">
+      <c r="D36" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E35" s="56" t="inlineStr">
+      <c r="E36" s="56" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="55" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="55" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B36" s="55" t="inlineStr">
+      <c r="B37" s="55" t="inlineStr">
         <is>
           <t>ASISTENTE PREDIAL</t>
         </is>
       </c>
-      <c r="C36" s="55" t="inlineStr">
+      <c r="C37" s="55" t="inlineStr">
         <is>
           <t>G13</t>
         </is>
       </c>
-      <c r="D36" s="55" t="inlineStr">
+      <c r="D37" s="55" t="inlineStr">
         <is>
           <t>asistente</t>
         </is>
       </c>
-      <c r="E36" s="55" t="inlineStr">
+      <c r="E37" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="56" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="56" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B37" s="56" t="inlineStr">
+      <c r="B38" s="56" t="inlineStr">
         <is>
           <t>NOMBRE DEL ASISTENTE</t>
         </is>
       </c>
-      <c r="C37" s="56" t="inlineStr">
+      <c r="C38" s="56" t="inlineStr">
         <is>
           <t>S13</t>
         </is>
       </c>
-      <c r="D37" s="56" t="inlineStr">
+      <c r="D38" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="56" t="inlineStr">
+      <c r="E38" s="56" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="55" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="55" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B38" s="55" t="inlineStr">
+      <c r="B39" s="55" t="inlineStr">
         <is>
           <t>CÓDIGO DE LA UNIDAD (BLOQUE / LOTE SUS)</t>
         </is>
       </c>
-      <c r="C38" s="55" t="inlineStr">
+      <c r="C39" s="55" t="inlineStr">
         <is>
           <t>G14</t>
         </is>
       </c>
-      <c r="D38" s="55" t="inlineStr">
+      <c r="D39" s="55" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
       </c>
-      <c r="E38" s="55" t="inlineStr">
+      <c r="E39" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="56" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="56" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B39" s="56" t="inlineStr">
+      <c r="B40" s="56" t="inlineStr">
         <is>
           <t>TIPO DE UNIDAD</t>
         </is>
       </c>
-      <c r="C39" s="56" t="inlineStr">
+      <c r="C40" s="56" t="inlineStr">
         <is>
           <t>S14</t>
         </is>
       </c>
-      <c r="D39" s="56" t="inlineStr">
+      <c r="D40" s="56" t="inlineStr">
         <is>
           <t>tipo_unidad (calculado)</t>
         </is>
       </c>
-      <c r="E39" s="56" t="inlineStr">
+      <c r="E40" s="56" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="55" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="55" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B40" s="55" t="inlineStr">
+      <c r="B41" s="55" t="inlineStr">
         <is>
           <t>UBICACIÓN SEGÚN CATÁLOGO V6</t>
         </is>
       </c>
-      <c r="C40" s="55" t="inlineStr">
+      <c r="C41" s="55" t="inlineStr">
         <is>
           <t>G15</t>
         </is>
       </c>
-      <c r="D40" s="55" t="inlineStr">
+      <c r="D41" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="55" t="inlineStr">
+      <c r="E41" s="55" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="56" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B41" s="56" t="inlineStr">
+      <c r="B42" s="56" t="inlineStr">
         <is>
           <t>ÁREA DE LA UNIDAD (ha)</t>
         </is>
       </c>
-      <c r="C41" s="56" t="inlineStr">
+      <c r="C42" s="56" t="inlineStr">
         <is>
           <t>S15</t>
         </is>
       </c>
-      <c r="D41" s="56" t="inlineStr">
+      <c r="D42" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E41" s="56" t="inlineStr">
+      <c r="E42" s="56" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="55" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="55" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B42" s="55" t="inlineStr">
+      <c r="B43" s="55" t="inlineStr">
         <is>
           <t>N° DE PREDIO EN LA UNIDAD</t>
         </is>
       </c>
-      <c r="C42" s="55" t="inlineStr">
+      <c r="C43" s="55" t="inlineStr">
         <is>
           <t>G16</t>
         </is>
       </c>
-      <c r="D42" s="55" t="inlineStr">
+      <c r="D43" s="55" t="inlineStr">
         <is>
           <t>n_predio</t>
         </is>
       </c>
-      <c r="E42" s="55" t="inlineStr">
+      <c r="E43" s="55" t="inlineStr">
         <is>
           <t>Número entero</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="56" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="56" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B43" s="56" t="inlineStr">
+      <c r="B44" s="56" t="inlineStr">
         <is>
           <t>CÓDIGO DE PREDIO</t>
         </is>
       </c>
-      <c r="C43" s="56" t="inlineStr">
+      <c r="C44" s="56" t="inlineStr">
         <is>
           <t>S16</t>
         </is>
       </c>
-      <c r="D43" s="56" t="inlineStr">
+      <c r="D44" s="56" t="inlineStr">
         <is>
           <t>cod_predio (calculado)</t>
         </is>
       </c>
-      <c r="E43" s="56" t="inlineStr">
+      <c r="E44" s="56" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="55" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="55" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B44" s="55" t="inlineStr">
+      <c r="B45" s="55" t="inlineStr">
         <is>
           <t>FECHA DE INSPECCIÓN</t>
         </is>
       </c>
-      <c r="C44" s="55" t="inlineStr">
+      <c r="C45" s="55" t="inlineStr">
         <is>
           <t>G17</t>
         </is>
       </c>
-      <c r="D44" s="55" t="inlineStr">
+      <c r="D45" s="55" t="inlineStr">
         <is>
           <t>fecha_insp (F-LA-03)</t>
         </is>
       </c>
-      <c r="E44" s="55" t="inlineStr">
+      <c r="E45" s="55" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="56" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="56" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B45" s="56" t="inlineStr">
+      <c r="B46" s="56" t="inlineStr">
         <is>
           <t>FECHA DE REGISTRO</t>
         </is>
       </c>
-      <c r="C45" s="56" t="inlineStr">
+      <c r="C46" s="56" t="inlineStr">
         <is>
           <t>S17</t>
         </is>
       </c>
-      <c r="D45" s="56" t="inlineStr">
+      <c r="D46" s="56" t="inlineStr">
         <is>
           <t>hoy</t>
         </is>
       </c>
-      <c r="E45" s="56" t="inlineStr">
+      <c r="E46" s="56" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="55" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="55" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B46" s="55" t="inlineStr">
+      <c r="B47" s="55" t="inlineStr">
         <is>
           <t>CONSENTIMIENTO USO DE DATOS PERSONALES (LEY 29733)</t>
         </is>
       </c>
-      <c r="C46" s="55" t="inlineStr">
+      <c r="C47" s="55" t="inlineStr">
         <is>
           <t>G18</t>
         </is>
       </c>
-      <c r="D46" s="55" t="inlineStr">
+      <c r="D47" s="55" t="inlineStr">
         <is>
           <t>consentimiento</t>
         </is>
       </c>
-      <c r="E46" s="55" t="inlineStr">
+      <c r="E47" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="56" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="56" t="inlineStr">
         <is>
           <t>DATOS GENERALES</t>
         </is>
       </c>
-      <c r="B47" s="56" t="inlineStr">
+      <c r="B48" s="56" t="inlineStr">
         <is>
           <t>CONTROL DE ASIGNACIÓN</t>
         </is>
       </c>
-      <c r="C47" s="56" t="inlineStr">
+      <c r="C48" s="56" t="inlineStr">
         <is>
           <t>S18</t>
         </is>
       </c>
-      <c r="D47" s="56" t="inlineStr">
+      <c r="D48" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E47" s="56" t="inlineStr">
+      <c r="E48" s="56" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="55" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="55" t="inlineStr">
         <is>
           <t>1. CONTROL E IDENTIFICACIÓN DEL PREDIO MATRIZ (TITULARIDAD REGISTRAL)</t>
         </is>
       </c>
-      <c r="B48" s="55" t="inlineStr">
+      <c r="B49" s="55" t="inlineStr">
         <is>
           <t>SITUACIÓN REGISTRAL</t>
         </is>
       </c>
-      <c r="C48" s="55" t="inlineStr">
+      <c r="C49" s="55" t="inlineStr">
         <is>
           <t>G21</t>
         </is>
       </c>
-      <c r="D48" s="55" t="inlineStr">
+      <c r="D49" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E48" s="55" t="inlineStr">
+      <c r="E49" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="56" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="56" t="inlineStr">
         <is>
           <t>1. CONTROL E IDENTIFICACIÓN DEL PREDIO MATRIZ (TITULARIDAD REGISTRAL)</t>
         </is>
       </c>
-      <c r="B49" s="56" t="inlineStr">
+      <c r="B50" s="56" t="inlineStr">
         <is>
           <t>PARTIDA ELECTRÓNICA / N° TÍTULO</t>
         </is>
       </c>
-      <c r="C49" s="56" t="inlineStr">
+      <c r="C50" s="56" t="inlineStr">
         <is>
           <t>S21</t>
         </is>
       </c>
-      <c r="D49" s="56" t="inlineStr">
+      <c r="D50" s="56" t="inlineStr">
         <is>
           <t>doc_partida</t>
         </is>
       </c>
-      <c r="E49" s="56" t="inlineStr">
+      <c r="E50" s="56" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="55" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="55" t="inlineStr">
         <is>
           <t>1. CONTROL E IDENTIFICACIÓN DEL PREDIO MATRIZ (TITULARIDAD REGISTRAL)</t>
         </is>
       </c>
-      <c r="B50" s="55" t="inlineStr">
+      <c r="B51" s="55" t="inlineStr">
         <is>
           <t>TIPO DE PERSONERÍA (TITULAR REGISTRAL)</t>
         </is>
       </c>
-      <c r="C50" s="55" t="inlineStr">
+      <c r="C51" s="55" t="inlineStr">
         <is>
           <t>G22</t>
         </is>
       </c>
-      <c r="D50" s="55" t="inlineStr">
+      <c r="D51" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E50" s="55" t="inlineStr">
+      <c r="E51" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="56" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="56" t="inlineStr">
         <is>
           <t>1. CONTROL E IDENTIFICACIÓN DEL PREDIO MATRIZ (TITULARIDAD REGISTRAL)</t>
         </is>
       </c>
-      <c r="B51" s="56" t="inlineStr">
+      <c r="B52" s="56" t="inlineStr">
         <is>
           <t>OFICINA REGISTRAL</t>
         </is>
       </c>
-      <c r="C51" s="56" t="inlineStr">
+      <c r="C52" s="56" t="inlineStr">
         <is>
           <t>S22</t>
         </is>
       </c>
-      <c r="D51" s="56" t="inlineStr">
+      <c r="D52" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E51" s="56" t="inlineStr">
+      <c r="E52" s="56" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="55" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="55" t="inlineStr">
         <is>
           <t>1. CONTROL E IDENTIFICACIÓN DEL PREDIO MATRIZ (TITULARIDAD REGISTRAL)</t>
         </is>
       </c>
-      <c r="B52" s="55" t="inlineStr">
+      <c r="B53" s="55" t="inlineStr">
         <is>
           <t>TITULAR REGISTRAL (NOMBRE / RAZÓN SOCIAL)</t>
         </is>
       </c>
-      <c r="C52" s="55" t="inlineStr">
+      <c r="C53" s="55" t="inlineStr">
         <is>
           <t>G23</t>
         </is>
       </c>
-      <c r="D52" s="55" t="inlineStr">
+      <c r="D53" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E52" s="55" t="inlineStr">
+      <c r="E53" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="56" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="56" t="inlineStr">
         <is>
           <t>1. CONTROL E IDENTIFICACIÓN DEL PREDIO MATRIZ (TITULARIDAD REGISTRAL)</t>
         </is>
       </c>
-      <c r="B53" s="56" t="inlineStr">
+      <c r="B54" s="56" t="inlineStr">
         <is>
           <t>Documentos exhibidos</t>
         </is>
       </c>
-      <c r="C53" s="56" t="inlineStr">
+      <c r="C54" s="56" t="inlineStr">
         <is>
           <t>G24:Y24</t>
         </is>
       </c>
-      <c r="D53" s="56" t="inlineStr">
+      <c r="D54" s="56" t="inlineStr">
         <is>
           <t>docs_exhibidos (selección múltiple)</t>
         </is>
       </c>
-      <c r="E53" s="56" t="inlineStr">
+      <c r="E54" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="55" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B54" s="55" t="inlineStr">
+      <c r="B55" s="55" t="inlineStr">
         <is>
           <t>CONDICIÓN JURÍDICA DEL PREDIANTE</t>
         </is>
       </c>
-      <c r="C54" s="55" t="inlineStr">
+      <c r="C55" s="55" t="inlineStr">
         <is>
           <t>G27</t>
         </is>
       </c>
-      <c r="D54" s="55" t="inlineStr">
+      <c r="D55" s="55" t="inlineStr">
         <is>
           <t>tipo_titularidad</t>
         </is>
       </c>
-      <c r="E54" s="55" t="inlineStr">
+      <c r="E55" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="56" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B55" s="56" t="inlineStr">
+      <c r="B56" s="56" t="inlineStr">
         <is>
           <t>TIPO DE PERSONERÍA</t>
         </is>
       </c>
-      <c r="C55" s="56" t="inlineStr">
+      <c r="C56" s="56" t="inlineStr">
         <is>
           <t>S27</t>
         </is>
       </c>
-      <c r="D55" s="56" t="inlineStr">
+      <c r="D56" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E55" s="56" t="inlineStr">
+      <c r="E56" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="55" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B56" s="55" t="inlineStr">
+      <c r="B57" s="55" t="inlineStr">
         <is>
           <t>ESTADO DE LA SUCESIÓN (si aplica)</t>
         </is>
       </c>
-      <c r="C56" s="55" t="inlineStr">
+      <c r="C57" s="55" t="inlineStr">
         <is>
           <t>G28</t>
         </is>
       </c>
-      <c r="D56" s="55" t="inlineStr">
+      <c r="D57" s="55" t="inlineStr">
         <is>
           <t>sucesion_estado</t>
         </is>
       </c>
-      <c r="E56" s="55" t="inlineStr">
+      <c r="E57" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="56" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B57" s="56" t="inlineStr">
+      <c r="B58" s="56" t="inlineStr">
         <is>
           <t>ALERTA / COHERENCIA</t>
         </is>
       </c>
-      <c r="C57" s="56" t="inlineStr">
+      <c r="C58" s="56" t="inlineStr">
         <is>
           <t>S28</t>
         </is>
       </c>
-      <c r="D57" s="56" t="inlineStr">
+      <c r="D58" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E57" s="56" t="inlineStr">
+      <c r="E58" s="56" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="55" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B58" s="55" t="inlineStr">
+      <c r="B59" s="55" t="inlineStr">
         <is>
           <t>NOMBRES</t>
         </is>
       </c>
-      <c r="C58" s="55" t="inlineStr">
+      <c r="C59" s="55" t="inlineStr">
         <is>
           <t>G30</t>
         </is>
       </c>
-      <c r="D58" s="55" t="inlineStr">
+      <c r="D59" s="55" t="inlineStr">
         <is>
           <t>tit_nombres</t>
         </is>
       </c>
-      <c r="E58" s="55" t="inlineStr">
+      <c r="E59" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="56" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B59" s="56" t="inlineStr">
+      <c r="B60" s="56" t="inlineStr">
         <is>
           <t>APELLIDOS</t>
         </is>
       </c>
-      <c r="C59" s="56" t="inlineStr">
+      <c r="C60" s="56" t="inlineStr">
         <is>
           <t>S30</t>
         </is>
       </c>
-      <c r="D59" s="56" t="inlineStr">
+      <c r="D60" s="56" t="inlineStr">
         <is>
           <t>tit_apellidos</t>
         </is>
       </c>
-      <c r="E59" s="56" t="inlineStr">
+      <c r="E60" s="56" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="55" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B60" s="55" t="inlineStr">
+      <c r="B61" s="55" t="inlineStr">
         <is>
           <t>DNI</t>
         </is>
       </c>
-      <c r="C60" s="55" t="inlineStr">
+      <c r="C61" s="55" t="inlineStr">
         <is>
           <t>G31</t>
         </is>
       </c>
-      <c r="D60" s="55" t="inlineStr">
+      <c r="D61" s="55" t="inlineStr">
         <is>
           <t>tit_dni</t>
         </is>
       </c>
-      <c r="E60" s="55" t="inlineStr">
+      <c r="E61" s="55" t="inlineStr">
         <is>
           <t>DNI (8 dígitos)</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="56" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B61" s="56" t="inlineStr">
+      <c r="B62" s="56" t="inlineStr">
         <is>
           <t>CELULAR</t>
         </is>
       </c>
-      <c r="C61" s="56" t="inlineStr">
+      <c r="C62" s="56" t="inlineStr">
         <is>
           <t>S31</t>
         </is>
       </c>
-      <c r="D61" s="56" t="inlineStr">
+      <c r="D62" s="56" t="inlineStr">
         <is>
           <t>tit_celular</t>
         </is>
       </c>
-      <c r="E61" s="56" t="inlineStr">
+      <c r="E62" s="56" t="inlineStr">
         <is>
           <t>Celular (9 dígitos)</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="55" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B62" s="55" t="inlineStr">
+      <c r="B63" s="55" t="inlineStr">
         <is>
           <t>ESTADO CIVIL</t>
         </is>
       </c>
-      <c r="C62" s="55" t="inlineStr">
+      <c r="C63" s="55" t="inlineStr">
         <is>
           <t>G32</t>
         </is>
       </c>
-      <c r="D62" s="55" t="inlineStr">
+      <c r="D63" s="55" t="inlineStr">
         <is>
           <t>tit_estado_civil</t>
         </is>
       </c>
-      <c r="E62" s="55" t="inlineStr">
+      <c r="E63" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="56" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B63" s="56" t="inlineStr">
+      <c r="B64" s="56" t="inlineStr">
         <is>
           <t>CORREO ELECTRÓNICO (opcional)</t>
         </is>
       </c>
-      <c r="C63" s="56" t="inlineStr">
+      <c r="C64" s="56" t="inlineStr">
         <is>
           <t>S32</t>
         </is>
       </c>
-      <c r="D63" s="56" t="inlineStr">
+      <c r="D64" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E63" s="56" t="inlineStr">
+      <c r="E64" s="56" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="55" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B64" s="55" t="inlineStr">
+      <c r="B65" s="55" t="inlineStr">
         <is>
           <t>CÓNYUGE / CONVIVIENTE</t>
         </is>
       </c>
-      <c r="C64" s="55" t="inlineStr">
+      <c r="C65" s="55" t="inlineStr">
         <is>
           <t>G33</t>
         </is>
       </c>
-      <c r="D64" s="55" t="inlineStr">
+      <c r="D65" s="55" t="inlineStr">
         <is>
           <t>cony_nombre</t>
         </is>
       </c>
-      <c r="E64" s="55" t="inlineStr">
+      <c r="E65" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="56" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B65" s="56" t="inlineStr">
+      <c r="B66" s="56" t="inlineStr">
         <is>
           <t>DNI DEL CÓNYUGE</t>
         </is>
       </c>
-      <c r="C65" s="56" t="inlineStr">
+      <c r="C66" s="56" t="inlineStr">
         <is>
           <t>S33</t>
         </is>
       </c>
-      <c r="D65" s="56" t="inlineStr">
+      <c r="D66" s="56" t="inlineStr">
         <is>
           <t>cony_dni</t>
         </is>
       </c>
-      <c r="E65" s="56" t="inlineStr">
+      <c r="E66" s="56" t="inlineStr">
         <is>
           <t>DNI (8 dígitos)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="55" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B66" s="55" t="inlineStr">
+      <c r="B67" s="55" t="inlineStr">
         <is>
           <t>COMUNIDAD / ENTIDAD / RAZÓN SOCIAL</t>
         </is>
       </c>
-      <c r="C66" s="55" t="inlineStr">
+      <c r="C67" s="55" t="inlineStr">
         <is>
           <t>G35</t>
         </is>
       </c>
-      <c r="D66" s="55" t="inlineStr">
+      <c r="D67" s="55" t="inlineStr">
         <is>
           <t>cc_nombre / est_entidad</t>
         </is>
       </c>
-      <c r="E66" s="55" t="inlineStr">
+      <c r="E67" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="56" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B67" s="56" t="inlineStr">
+      <c r="B68" s="56" t="inlineStr">
         <is>
           <t>RUC</t>
         </is>
       </c>
-      <c r="C67" s="56" t="inlineStr">
+      <c r="C68" s="56" t="inlineStr">
         <is>
           <t>G36</t>
         </is>
       </c>
-      <c r="D67" s="56" t="inlineStr">
+      <c r="D68" s="56" t="inlineStr">
         <is>
           <t>cc_ruc</t>
         </is>
       </c>
-      <c r="E67" s="56" t="inlineStr">
+      <c r="E68" s="56" t="inlineStr">
         <is>
           <t>RUC (11 dígitos)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="55" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B68" s="55" t="inlineStr">
+      <c r="B69" s="55" t="inlineStr">
         <is>
           <t>PARTIDA REGISTRAL (SUNARP)</t>
         </is>
       </c>
-      <c r="C68" s="55" t="inlineStr">
+      <c r="C69" s="55" t="inlineStr">
         <is>
           <t>S36</t>
         </is>
       </c>
-      <c r="D68" s="55" t="inlineStr">
+      <c r="D69" s="55" t="inlineStr">
         <is>
           <t>cc_partida</t>
         </is>
       </c>
-      <c r="E68" s="55" t="inlineStr">
+      <c r="E69" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="56" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B69" s="56" t="inlineStr">
+      <c r="B70" s="56" t="inlineStr">
         <is>
           <t>REPRESENTANTE / PRESIDENTE COMUNAL</t>
         </is>
       </c>
-      <c r="C69" s="56" t="inlineStr">
+      <c r="C70" s="56" t="inlineStr">
         <is>
           <t>G37</t>
         </is>
       </c>
-      <c r="D69" s="56" t="inlineStr">
+      <c r="D70" s="56" t="inlineStr">
         <is>
           <t>cc_presidente / est_contacto</t>
         </is>
       </c>
-      <c r="E69" s="56" t="inlineStr">
+      <c r="E70" s="56" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="55" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B70" s="55" t="inlineStr">
+      <c r="B71" s="55" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="C70" s="55" t="inlineStr">
+      <c r="C71" s="55" t="inlineStr">
         <is>
           <t>S37</t>
         </is>
       </c>
-      <c r="D70" s="55" t="inlineStr">
+      <c r="D71" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E70" s="55" t="inlineStr">
+      <c r="E71" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="56" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B71" s="56" t="inlineStr">
+      <c r="B72" s="56" t="inlineStr">
         <is>
           <t>DNI DEL REPRESENTANTE</t>
         </is>
       </c>
-      <c r="C71" s="56" t="inlineStr">
+      <c r="C72" s="56" t="inlineStr">
         <is>
           <t>G38</t>
         </is>
       </c>
-      <c r="D71" s="56" t="inlineStr">
+      <c r="D72" s="56" t="inlineStr">
         <is>
           <t>cc_presidente_dni</t>
         </is>
       </c>
-      <c r="E71" s="56" t="inlineStr">
+      <c r="E72" s="56" t="inlineStr">
         <is>
           <t>DNI (8 dígitos)</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="55" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="55" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B72" s="55" t="inlineStr">
+      <c r="B73" s="55" t="inlineStr">
         <is>
           <t>CELULAR DEL REPRESENTANTE</t>
         </is>
       </c>
-      <c r="C72" s="55" t="inlineStr">
+      <c r="C73" s="55" t="inlineStr">
         <is>
           <t>S38</t>
         </is>
       </c>
-      <c r="D72" s="55" t="inlineStr">
+      <c r="D73" s="55" t="inlineStr">
         <is>
           <t>cc_presidente_cel</t>
         </is>
       </c>
-      <c r="E72" s="55" t="inlineStr">
+      <c r="E73" s="55" t="inlineStr">
         <is>
           <t>Celular (9 dígitos)</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="56" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="56" t="inlineStr">
         <is>
           <t>2. IDENTIFICACIÓN DEL PREDIANTE Y TENENCIA</t>
         </is>
       </c>
-      <c r="B73" s="56" t="inlineStr">
+      <c r="B74" s="56" t="inlineStr">
         <is>
           <t>Domicilio (dirección, distrito, provincia, departamento)</t>
         </is>
       </c>
-      <c r="C73" s="56" t="inlineStr">
+      <c r="C74" s="56" t="inlineStr">
         <is>
           <t>B41:Y41</t>
         </is>
       </c>
-      <c r="D73" s="56" t="inlineStr">
+      <c r="D74" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E73" s="56" t="inlineStr">
+      <c r="E74" s="56" t="inlineStr">
         <is>
           <t>Texto / lista abierta</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="55" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="55" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B74" s="55" t="inlineStr">
+      <c r="B75" s="55" t="inlineStr">
         <is>
           <t>NOMBRE DEL PREDIO</t>
         </is>
       </c>
-      <c r="C74" s="55" t="inlineStr">
+      <c r="C75" s="55" t="inlineStr">
         <is>
           <t>G44</t>
         </is>
       </c>
-      <c r="D74" s="55" t="inlineStr">
+      <c r="D75" s="55" t="inlineStr">
         <is>
           <t>predio_nombre</t>
         </is>
       </c>
-      <c r="E74" s="55" t="inlineStr">
+      <c r="E75" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="56" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="56" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B75" s="56" t="inlineStr">
+      <c r="B76" s="56" t="inlineStr">
         <is>
           <t>CENTRO POBLADO / SECTOR</t>
         </is>
       </c>
-      <c r="C75" s="56" t="inlineStr">
+      <c r="C76" s="56" t="inlineStr">
         <is>
           <t>G45</t>
         </is>
       </c>
-      <c r="D75" s="56" t="inlineStr">
+      <c r="D76" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E75" s="56" t="inlineStr">
+      <c r="E76" s="56" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="55" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="55" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B76" s="55" t="inlineStr">
+      <c r="B77" s="55" t="inlineStr">
         <is>
           <t>COMUNIDAD CAMPESINA (si aplica)</t>
         </is>
       </c>
-      <c r="C76" s="55" t="inlineStr">
+      <c r="C77" s="55" t="inlineStr">
         <is>
           <t>S45</t>
         </is>
       </c>
-      <c r="D76" s="55" t="inlineStr">
+      <c r="D77" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E76" s="55" t="inlineStr">
+      <c r="E77" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="56" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="56" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B77" s="56" t="inlineStr">
+      <c r="B78" s="56" t="inlineStr">
         <is>
           <t>REFERENCIA DE ACCESO</t>
         </is>
       </c>
-      <c r="C77" s="56" t="inlineStr">
+      <c r="C78" s="56" t="inlineStr">
         <is>
           <t>G46</t>
         </is>
       </c>
-      <c r="D77" s="56" t="inlineStr">
+      <c r="D78" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E77" s="56" t="inlineStr">
+      <c r="E78" s="56" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="55" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="55" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B78" s="55" t="inlineStr">
+      <c r="B79" s="55" t="inlineStr">
         <is>
           <t>TIPO DE ACCESO</t>
         </is>
       </c>
-      <c r="C78" s="55" t="inlineStr">
+      <c r="C79" s="55" t="inlineStr">
         <is>
           <t>G47</t>
         </is>
       </c>
-      <c r="D78" s="55" t="inlineStr">
+      <c r="D79" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E78" s="55" t="inlineStr">
+      <c r="E79" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="56" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="56" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B79" s="56" t="inlineStr">
+      <c r="B80" s="56" t="inlineStr">
         <is>
           <t>TIEMPO DESDE EL C.P. (min)</t>
         </is>
       </c>
-      <c r="C79" s="56" t="inlineStr">
+      <c r="C80" s="56" t="inlineStr">
         <is>
           <t>S47</t>
         </is>
       </c>
-      <c r="D79" s="56" t="inlineStr">
+      <c r="D80" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E79" s="56" t="inlineStr">
+      <c r="E80" s="56" t="inlineStr">
         <is>
           <t>Número entero</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="55" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="55" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B80" s="55" t="inlineStr">
+      <c r="B81" s="55" t="inlineStr">
         <is>
           <t>SISTEMA DE COORDENADAS</t>
         </is>
       </c>
-      <c r="C80" s="55" t="inlineStr">
+      <c r="C81" s="55" t="inlineStr">
         <is>
           <t>G48</t>
         </is>
       </c>
-      <c r="D80" s="55" t="inlineStr">
+      <c r="D81" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E80" s="55" t="inlineStr">
+      <c r="E81" s="55" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="56" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="56" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B81" s="56" t="inlineStr">
+      <c r="B82" s="56" t="inlineStr">
         <is>
           <t>ESTE UTM (m)</t>
         </is>
       </c>
-      <c r="C81" s="56" t="inlineStr">
+      <c r="C82" s="56" t="inlineStr">
         <is>
           <t>G49</t>
         </is>
       </c>
-      <c r="D81" s="56" t="inlineStr">
+      <c r="D82" s="56" t="inlineStr">
         <is>
           <t>punto_interior (Este)</t>
         </is>
       </c>
-      <c r="E81" s="56" t="inlineStr">
+      <c r="E82" s="56" t="inlineStr">
         <is>
           <t>Número</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="55" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="55" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B82" s="55" t="inlineStr">
+      <c r="B83" s="55" t="inlineStr">
         <is>
           <t>NORTE UTM (m)</t>
         </is>
       </c>
-      <c r="C82" s="55" t="inlineStr">
+      <c r="C83" s="55" t="inlineStr">
         <is>
           <t>S49</t>
         </is>
       </c>
-      <c r="D82" s="55" t="inlineStr">
+      <c r="D83" s="55" t="inlineStr">
         <is>
           <t>punto_interior (Norte)</t>
         </is>
       </c>
-      <c r="E82" s="55" t="inlineStr">
+      <c r="E83" s="55" t="inlineStr">
         <is>
           <t>Número</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="56" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="56" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B83" s="56" t="inlineStr">
+      <c r="B84" s="56" t="inlineStr">
         <is>
           <t>ALTITUD (m s.n.m.)</t>
         </is>
       </c>
-      <c r="C83" s="56" t="inlineStr">
+      <c r="C84" s="56" t="inlineStr">
         <is>
           <t>G50</t>
         </is>
       </c>
-      <c r="D83" s="56" t="inlineStr">
+      <c r="D84" s="56" t="inlineStr">
         <is>
           <t>punto_interior (alt)</t>
         </is>
       </c>
-      <c r="E83" s="56" t="inlineStr">
+      <c r="E84" s="56" t="inlineStr">
         <is>
           <t>Número</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="55" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="55" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B84" s="55" t="inlineStr">
+      <c r="B85" s="55" t="inlineStr">
         <is>
           <t>PRECISIÓN GPS (m)</t>
         </is>
       </c>
-      <c r="C84" s="55" t="inlineStr">
+      <c r="C85" s="55" t="inlineStr">
         <is>
           <t>S50</t>
         </is>
       </c>
-      <c r="D84" s="55" t="inlineStr">
+      <c r="D85" s="55" t="inlineStr">
         <is>
           <t>punto_interior (prec)</t>
         </is>
       </c>
-      <c r="E84" s="55" t="inlineStr">
+      <c r="E85" s="55" t="inlineStr">
         <is>
           <t>Número</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="56" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="56" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B85" s="56" t="inlineStr">
+      <c r="B86" s="56" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C85" s="56" t="inlineStr">
+      <c r="C86" s="56" t="inlineStr">
         <is>
           <t>G51</t>
         </is>
       </c>
-      <c r="D85" s="56" t="inlineStr">
+      <c r="D86" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E85" s="56" t="inlineStr">
+      <c r="E86" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="55" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="55" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B86" s="55" t="inlineStr">
+      <c r="B87" s="55" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="C86" s="55" t="inlineStr">
+      <c r="C87" s="55" t="inlineStr">
         <is>
           <t>S51</t>
         </is>
       </c>
-      <c r="D86" s="55" t="inlineStr">
+      <c r="D87" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E86" s="55" t="inlineStr">
+      <c r="E87" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="56" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="56" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B87" s="56" t="inlineStr">
+      <c r="B88" s="56" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="C87" s="56" t="inlineStr">
+      <c r="C88" s="56" t="inlineStr">
         <is>
           <t>G52</t>
         </is>
       </c>
-      <c r="D87" s="56" t="inlineStr">
+      <c r="D88" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E87" s="56" t="inlineStr">
+      <c r="E88" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="55" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="55" t="inlineStr">
         <is>
           <t>3. DESCRIPCIÓN GENERAL DEL PREDIO INTERVENIDO</t>
         </is>
       </c>
-      <c r="B88" s="55" t="inlineStr">
+      <c r="B89" s="55" t="inlineStr">
         <is>
           <t>VERIFICACIÓN CON CATÁLOGO V6</t>
         </is>
       </c>
-      <c r="C88" s="55" t="inlineStr">
+      <c r="C89" s="55" t="inlineStr">
         <is>
           <t>S52</t>
         </is>
       </c>
-      <c r="D88" s="55" t="inlineStr">
+      <c r="D89" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E88" s="55" t="inlineStr">
+      <c r="E89" s="55" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="56" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B89" s="56" t="inlineStr">
+      <c r="B90" s="56" t="inlineStr">
         <is>
           <t>USO ACTUAL DEL SUELO</t>
         </is>
       </c>
-      <c r="C89" s="56" t="inlineStr">
+      <c r="C90" s="56" t="inlineStr">
         <is>
           <t>G55</t>
         </is>
       </c>
-      <c r="D89" s="56" t="inlineStr">
+      <c r="D90" s="56" t="inlineStr">
         <is>
           <t>uso_actual / uso_observado</t>
         </is>
       </c>
-      <c r="E89" s="56" t="inlineStr">
+      <c r="E90" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="55" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B90" s="55" t="inlineStr">
+      <c r="B91" s="55" t="inlineStr">
         <is>
           <t>ESPECIFIQUE SI ES «OTRO»</t>
         </is>
       </c>
-      <c r="C90" s="55" t="inlineStr">
+      <c r="C91" s="55" t="inlineStr">
         <is>
           <t>S55</t>
         </is>
       </c>
-      <c r="D90" s="55" t="inlineStr">
+      <c r="D91" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E90" s="55" t="inlineStr">
+      <c r="E91" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="56" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B91" s="56" t="inlineStr">
+      <c r="B92" s="56" t="inlineStr">
         <is>
           <t>OCUPACIÓN OBSERVADA</t>
         </is>
       </c>
-      <c r="C91" s="56" t="inlineStr">
+      <c r="C92" s="56" t="inlineStr">
         <is>
           <t>G56</t>
         </is>
       </c>
-      <c r="D91" s="56" t="inlineStr">
+      <c r="D92" s="56" t="inlineStr">
         <is>
           <t>ocupacion</t>
         </is>
       </c>
-      <c r="E91" s="56" t="inlineStr">
+      <c r="E92" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="55" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B92" s="55" t="inlineStr">
+      <c r="B93" s="55" t="inlineStr">
         <is>
           <t>DETALLE DE LA OCUPACIÓN</t>
         </is>
       </c>
-      <c r="C92" s="55" t="inlineStr">
+      <c r="C93" s="55" t="inlineStr">
         <is>
           <t>S56</t>
         </is>
       </c>
-      <c r="D92" s="55" t="inlineStr">
+      <c r="D93" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E92" s="55" t="inlineStr">
+      <c r="E93" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="56" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B93" s="56" t="inlineStr">
+      <c r="B94" s="56" t="inlineStr">
         <is>
           <t>EDIFICACIONES / CULTIVOS</t>
         </is>
       </c>
-      <c r="C93" s="56" t="inlineStr">
+      <c r="C94" s="56" t="inlineStr">
         <is>
           <t>G57</t>
         </is>
       </c>
-      <c r="D93" s="56" t="inlineStr">
+      <c r="D94" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E93" s="56" t="inlineStr">
+      <c r="E94" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="55" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B94" s="55" t="inlineStr">
+      <c r="B95" s="55" t="inlineStr">
         <is>
           <t>DETALLE / ESPECIFIQUE «OTRO»</t>
         </is>
       </c>
-      <c r="C94" s="55" t="inlineStr">
+      <c r="C95" s="55" t="inlineStr">
         <is>
           <t>S57</t>
         </is>
       </c>
-      <c r="D94" s="55" t="inlineStr">
+      <c r="D95" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E94" s="55" t="inlineStr">
+      <c r="E95" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="56" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B95" s="56" t="inlineStr">
+      <c r="B96" s="56" t="inlineStr">
         <is>
           <t>TOPOGRAFÍA / PENDIENTE</t>
         </is>
       </c>
-      <c r="C95" s="56" t="inlineStr">
+      <c r="C96" s="56" t="inlineStr">
         <is>
           <t>G58</t>
         </is>
       </c>
-      <c r="D95" s="56" t="inlineStr">
+      <c r="D96" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E95" s="56" t="inlineStr">
+      <c r="E96" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="55" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B96" s="55" t="inlineStr">
+      <c r="B97" s="55" t="inlineStr">
         <is>
           <t>EROSIÓN OBSERVADA</t>
         </is>
       </c>
-      <c r="C96" s="55" t="inlineStr">
+      <c r="C97" s="55" t="inlineStr">
         <is>
           <t>S58</t>
         </is>
       </c>
-      <c r="D96" s="55" t="inlineStr">
+      <c r="D97" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E96" s="55" t="inlineStr">
+      <c r="E97" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="56" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B97" s="56" t="inlineStr">
+      <c r="B98" s="56" t="inlineStr">
         <is>
           <t>ESTADO DE LA COBERTURA VEGETAL</t>
         </is>
       </c>
-      <c r="C97" s="56" t="inlineStr">
+      <c r="C98" s="56" t="inlineStr">
         <is>
           <t>G59</t>
         </is>
       </c>
-      <c r="D97" s="56" t="inlineStr">
+      <c r="D98" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E97" s="56" t="inlineStr">
+      <c r="E98" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="55" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B98" s="55" t="inlineStr">
+      <c r="B99" s="55" t="inlineStr">
         <is>
           <t>EVIDENCIA DE MOVIMIENTOS EN MASA</t>
         </is>
       </c>
-      <c r="C98" s="55" t="inlineStr">
+      <c r="C99" s="55" t="inlineStr">
         <is>
           <t>S59</t>
         </is>
       </c>
-      <c r="D98" s="55" t="inlineStr">
+      <c r="D99" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E98" s="55" t="inlineStr">
+      <c r="E99" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="56" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B99" s="56" t="inlineStr">
+      <c r="B100" s="56" t="inlineStr">
         <is>
           <t>OTROS / DESCRIPCIÓN DEL PREDIO</t>
         </is>
       </c>
-      <c r="C99" s="56" t="inlineStr">
+      <c r="C100" s="56" t="inlineStr">
         <is>
           <t>G60</t>
         </is>
       </c>
-      <c r="D99" s="56" t="inlineStr">
+      <c r="D100" s="56" t="inlineStr">
         <is>
           <t>descripcion_predio (F-LA-03)</t>
         </is>
       </c>
-      <c r="E99" s="56" t="inlineStr">
+      <c r="E100" s="56" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="55" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B100" s="55" t="inlineStr">
+      <c r="B101" s="55" t="inlineStr">
         <is>
           <t>TIPO DE PREDIO</t>
         </is>
       </c>
-      <c r="C100" s="55" t="inlineStr">
+      <c r="C101" s="55" t="inlineStr">
         <is>
           <t>G62</t>
         </is>
       </c>
-      <c r="D100" s="55" t="inlineStr">
+      <c r="D101" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E100" s="55" t="inlineStr">
+      <c r="E101" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="56" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B101" s="56" t="inlineStr">
+      <c r="B102" s="56" t="inlineStr">
         <is>
           <t>ÁREA MATRIZ DEL PREDIO (ha)</t>
         </is>
       </c>
-      <c r="C101" s="56" t="inlineStr">
+      <c r="C102" s="56" t="inlineStr">
         <is>
           <t>S62</t>
         </is>
       </c>
-      <c r="D101" s="56" t="inlineStr">
+      <c r="D102" s="56" t="inlineStr">
         <is>
           <t>predio_area_decl_ha</t>
         </is>
       </c>
-      <c r="E101" s="56" t="inlineStr">
+      <c r="E102" s="56" t="inlineStr">
         <is>
           <t>Número</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="55" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B102" s="55" t="inlineStr">
+      <c r="B103" s="55" t="inlineStr">
         <is>
           <t>PERÍMETRO (m)</t>
         </is>
       </c>
-      <c r="C102" s="55" t="inlineStr">
+      <c r="C103" s="55" t="inlineStr">
         <is>
           <t>G63</t>
         </is>
       </c>
-      <c r="D102" s="55" t="inlineStr">
+      <c r="D103" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E102" s="55" t="inlineStr">
+      <c r="E103" s="55" t="inlineStr">
         <is>
           <t>Número</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="56" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B103" s="56" t="inlineStr">
+      <c r="B104" s="56" t="inlineStr">
         <is>
           <t>ÁREA MATRIZ DEL PREDIO (m²)</t>
         </is>
       </c>
-      <c r="C103" s="56" t="inlineStr">
+      <c r="C104" s="56" t="inlineStr">
         <is>
           <t>S63</t>
         </is>
       </c>
-      <c r="D103" s="56" t="inlineStr">
+      <c r="D104" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E103" s="56" t="inlineStr">
+      <c r="E104" s="56" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="55" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B104" s="55" t="inlineStr">
+      <c r="B105" s="55" t="inlineStr">
         <is>
           <t>Colindancia norte</t>
         </is>
       </c>
-      <c r="C104" s="55" t="inlineStr">
+      <c r="C105" s="55" t="inlineStr">
         <is>
           <t>F66:Y66</t>
         </is>
       </c>
-      <c r="D104" s="55" t="inlineStr">
+      <c r="D105" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E104" s="55" t="inlineStr">
+      <c r="E105" s="55" t="inlineStr">
         <is>
           <t>Texto / lista</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="56" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B105" s="56" t="inlineStr">
+      <c r="B106" s="56" t="inlineStr">
         <is>
           <t>Colindancia este</t>
         </is>
       </c>
-      <c r="C105" s="56" t="inlineStr">
+      <c r="C106" s="56" t="inlineStr">
         <is>
           <t>F67:Y67</t>
         </is>
       </c>
-      <c r="D105" s="56" t="inlineStr">
+      <c r="D106" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E105" s="56" t="inlineStr">
+      <c r="E106" s="56" t="inlineStr">
         <is>
           <t>Texto / lista</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="55" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B106" s="55" t="inlineStr">
+      <c r="B107" s="55" t="inlineStr">
         <is>
           <t>Colindancia sur</t>
         </is>
       </c>
-      <c r="C106" s="55" t="inlineStr">
+      <c r="C107" s="55" t="inlineStr">
         <is>
           <t>F68:Y68</t>
         </is>
       </c>
-      <c r="D106" s="55" t="inlineStr">
+      <c r="D107" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E106" s="55" t="inlineStr">
+      <c r="E107" s="55" t="inlineStr">
         <is>
           <t>Texto / lista</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="56" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="56" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B107" s="56" t="inlineStr">
+      <c r="B108" s="56" t="inlineStr">
         <is>
           <t>Colindancia oeste</t>
         </is>
       </c>
-      <c r="C107" s="56" t="inlineStr">
+      <c r="C108" s="56" t="inlineStr">
         <is>
           <t>F69:Y69</t>
         </is>
       </c>
-      <c r="D107" s="56" t="inlineStr">
+      <c r="D108" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E107" s="56" t="inlineStr">
+      <c r="E108" s="56" t="inlineStr">
         <is>
           <t>Texto / lista</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="55" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="55" t="inlineStr">
         <is>
           <t>4. DESCRIPCIÓN DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="B108" s="55" t="inlineStr">
+      <c r="B109" s="55" t="inlineStr">
         <is>
           <t>CONFLICTOS DE LINDEROS / OBSERVACIONES</t>
         </is>
       </c>
-      <c r="C108" s="55" t="inlineStr">
+      <c r="C109" s="55" t="inlineStr">
         <is>
           <t>G70</t>
         </is>
       </c>
-      <c r="D108" s="55" t="inlineStr">
+      <c r="D109" s="55" t="inlineStr">
         <is>
           <t>conflicto_linderos_det</t>
         </is>
       </c>
-      <c r="E108" s="55" t="inlineStr">
+      <c r="E109" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="56" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="56" t="inlineStr">
         <is>
           <t>5. DESCRIPCIÓN DEL ÁREA A INTERVENIR (DENTRO DE LA UNIDAD)</t>
         </is>
       </c>
-      <c r="B109" s="56" t="inlineStr">
+      <c r="B110" s="56" t="inlineStr">
         <is>
           <t>ÁREA DEL PREDIO DENTRO DE LA UNIDAD (ha)</t>
         </is>
       </c>
-      <c r="C109" s="56" t="inlineStr">
+      <c r="C110" s="56" t="inlineStr">
         <is>
           <t>G74</t>
         </is>
       </c>
-      <c r="D109" s="56" t="inlineStr">
+      <c r="D110" s="56" t="inlineStr">
         <is>
           <t>predio_area_unidad_ha</t>
         </is>
       </c>
-      <c r="E109" s="56" t="inlineStr">
+      <c r="E110" s="56" t="inlineStr">
         <is>
           <t>Número</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="55" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="55" t="inlineStr">
         <is>
           <t>5. DESCRIPCIÓN DEL ÁREA A INTERVENIR (DENTRO DE LA UNIDAD)</t>
         </is>
       </c>
-      <c r="B110" s="55" t="inlineStr">
+      <c r="B111" s="55" t="inlineStr">
         <is>
           <t>ÁREA DENTRO DE LA UNIDAD (m²)</t>
         </is>
       </c>
-      <c r="C110" s="55" t="inlineStr">
+      <c r="C111" s="55" t="inlineStr">
         <is>
           <t>S74</t>
         </is>
       </c>
-      <c r="D110" s="55" t="inlineStr">
+      <c r="D111" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E110" s="55" t="inlineStr">
+      <c r="E111" s="55" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="56" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="56" t="inlineStr">
         <is>
           <t>5. DESCRIPCIÓN DEL ÁREA A INTERVENIR (DENTRO DE LA UNIDAD)</t>
         </is>
       </c>
-      <c r="B111" s="56" t="inlineStr">
+      <c r="B112" s="56" t="inlineStr">
         <is>
           <t>% DEL PREDIO MATRIZ</t>
         </is>
       </c>
-      <c r="C111" s="56" t="inlineStr">
+      <c r="C112" s="56" t="inlineStr">
         <is>
           <t>G75</t>
         </is>
       </c>
-      <c r="D111" s="56" t="inlineStr">
+      <c r="D112" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E111" s="56" t="inlineStr">
+      <c r="E112" s="56" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="55" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="55" t="inlineStr">
         <is>
           <t>5. DESCRIPCIÓN DEL ÁREA A INTERVENIR (DENTRO DE LA UNIDAD)</t>
         </is>
       </c>
-      <c r="B112" s="55" t="inlineStr">
+      <c r="B113" s="55" t="inlineStr">
         <is>
           <t>CONTROL DE ÁREAS</t>
         </is>
       </c>
-      <c r="C112" s="55" t="inlineStr">
+      <c r="C113" s="55" t="inlineStr">
         <is>
           <t>S75</t>
         </is>
       </c>
-      <c r="D112" s="55" t="inlineStr">
+      <c r="D113" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E112" s="55" t="inlineStr">
+      <c r="E113" s="55" t="inlineStr">
         <is>
           <t>Automático</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="56" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="56" t="inlineStr">
         <is>
           <t>5. DESCRIPCIÓN DEL ÁREA A INTERVENIR (DENTRO DE LA UNIDAD)</t>
         </is>
       </c>
-      <c r="B113" s="56" t="inlineStr">
+      <c r="B114" s="56" t="inlineStr">
         <is>
           <t>Interferencias</t>
         </is>
       </c>
-      <c r="C113" s="56" t="inlineStr">
+      <c r="C114" s="56" t="inlineStr">
         <is>
           <t>G77:Y77</t>
         </is>
       </c>
-      <c r="D113" s="56" t="inlineStr">
+      <c r="D114" s="56" t="inlineStr">
         <is>
           <t>interferencias (selección múltiple)</t>
         </is>
       </c>
-      <c r="E113" s="56" t="inlineStr">
+      <c r="E114" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="55" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="55" t="inlineStr">
         <is>
           <t>5. DESCRIPCIÓN DEL ÁREA A INTERVENIR (DENTRO DE LA UNIDAD)</t>
         </is>
       </c>
-      <c r="B114" s="55" t="inlineStr">
+      <c r="B115" s="55" t="inlineStr">
         <is>
           <t>DETALLE DE INTERFERENCIAS</t>
         </is>
       </c>
-      <c r="C114" s="55" t="inlineStr">
+      <c r="C115" s="55" t="inlineStr">
         <is>
           <t>G78</t>
         </is>
       </c>
-      <c r="D114" s="55" t="inlineStr">
+      <c r="D115" s="55" t="inlineStr">
         <is>
           <t>interf_detalle</t>
         </is>
       </c>
-      <c r="E114" s="55" t="inlineStr">
+      <c r="E115" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="56" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="56" t="inlineStr">
         <is>
           <t>5. DESCRIPCIÓN DEL ÁREA A INTERVENIR (DENTRO DE LA UNIDAD)</t>
         </is>
       </c>
-      <c r="B115" s="56" t="inlineStr">
+      <c r="B116" s="56" t="inlineStr">
         <is>
           <t>Intervención prevista</t>
         </is>
       </c>
-      <c r="C115" s="56" t="inlineStr">
+      <c r="C116" s="56" t="inlineStr">
         <is>
           <t>G79:Y79</t>
         </is>
       </c>
-      <c r="D115" s="56" t="inlineStr">
+      <c r="D116" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E115" s="56" t="inlineStr">
+      <c r="E116" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="55" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="55" t="inlineStr">
         <is>
           <t>5. DESCRIPCIÓN DEL ÁREA A INTERVENIR (DENTRO DE LA UNIDAD)</t>
         </is>
       </c>
-      <c r="B116" s="55" t="inlineStr">
+      <c r="B117" s="55" t="inlineStr">
         <is>
           <t>Afectaciones OC-01 … OC-05</t>
         </is>
       </c>
-      <c r="C116" s="55" t="inlineStr">
+      <c r="C117" s="55" t="inlineStr">
         <is>
           <t>B82:Y86</t>
         </is>
       </c>
-      <c r="D116" s="55" t="inlineStr">
+      <c r="D117" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E116" s="55" t="inlineStr">
+      <c r="E117" s="55" t="inlineStr">
         <is>
           <t>Tabla</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="56" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="56" t="inlineStr">
         <is>
           <t>6. DISPONIBILIDAD Y CONDICIÓN DE LIBERACIÓN</t>
         </is>
       </c>
-      <c r="B117" s="56" t="inlineStr">
+      <c r="B118" s="56" t="inlineStr">
         <is>
           <t>ACEPTACIÓN DEL TITULAR / PREDIANTE</t>
         </is>
       </c>
-      <c r="C117" s="56" t="inlineStr">
+      <c r="C118" s="56" t="inlineStr">
         <is>
           <t>G89</t>
         </is>
       </c>
-      <c r="D117" s="56" t="inlineStr">
+      <c r="D118" s="56" t="inlineStr">
         <is>
           <t>aceptacion</t>
         </is>
       </c>
-      <c r="E117" s="56" t="inlineStr">
+      <c r="E118" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="55" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="55" t="inlineStr">
         <is>
           <t>6. DISPONIBILIDAD Y CONDICIÓN DE LIBERACIÓN</t>
         </is>
       </c>
-      <c r="B118" s="55" t="inlineStr">
+      <c r="B119" s="55" t="inlineStr">
         <is>
           <t>MODALIDAD DE DISPONIBILIDAD</t>
         </is>
       </c>
-      <c r="C118" s="55" t="inlineStr">
+      <c r="C119" s="55" t="inlineStr">
         <is>
           <t>S89</t>
         </is>
       </c>
-      <c r="D118" s="55" t="inlineStr">
+      <c r="D119" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E118" s="55" t="inlineStr">
+      <c r="E119" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="56" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="56" t="inlineStr">
         <is>
           <t>6. DISPONIBILIDAD Y CONDICIÓN DE LIBERACIÓN</t>
         </is>
       </c>
-      <c r="B119" s="56" t="inlineStr">
+      <c r="B120" s="56" t="inlineStr">
         <is>
           <t>CONCLUSIÓN DE CAMPO</t>
         </is>
       </c>
-      <c r="C119" s="56" t="inlineStr">
+      <c r="C120" s="56" t="inlineStr">
         <is>
           <t>G90</t>
         </is>
       </c>
-      <c r="D119" s="56" t="inlineStr">
+      <c r="D120" s="56" t="inlineStr">
         <is>
           <t>conclusion_campo (F-LA-03)</t>
         </is>
       </c>
-      <c r="E119" s="56" t="inlineStr">
+      <c r="E120" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="55" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="55" t="inlineStr">
         <is>
           <t>6. DISPONIBILIDAD Y CONDICIÓN DE LIBERACIÓN</t>
         </is>
       </c>
-      <c r="B120" s="55" t="inlineStr">
+      <c r="B121" s="55" t="inlineStr">
         <is>
           <t>ESTADO LA PROPUESTO</t>
         </is>
       </c>
-      <c r="C120" s="55" t="inlineStr">
+      <c r="C121" s="55" t="inlineStr">
         <is>
           <t>S90</t>
         </is>
       </c>
-      <c r="D120" s="55" t="inlineStr">
+      <c r="D121" s="55" t="inlineStr">
         <is>
           <t>estado_la_propuesto</t>
         </is>
       </c>
-      <c r="E120" s="55" t="inlineStr">
+      <c r="E121" s="55" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="56" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="56" t="inlineStr">
         <is>
           <t>6. DISPONIBILIDAD Y CONDICIÓN DE LIBERACIÓN</t>
         </is>
       </c>
-      <c r="B121" s="56" t="inlineStr">
+      <c r="B122" s="56" t="inlineStr">
         <is>
           <t>ACTA PREVISTA</t>
         </is>
       </c>
-      <c r="C121" s="56" t="inlineStr">
+      <c r="C122" s="56" t="inlineStr">
         <is>
           <t>G91</t>
         </is>
       </c>
-      <c r="D121" s="56" t="inlineStr">
+      <c r="D122" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E121" s="56" t="inlineStr">
+      <c r="E122" s="56" t="inlineStr">
         <is>
           <t>Lista desplegable</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="55" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="55" t="inlineStr">
         <is>
           <t>6. DISPONIBILIDAD Y CONDICIÓN DE LIBERACIÓN</t>
         </is>
       </c>
-      <c r="B122" s="55" t="inlineStr">
+      <c r="B123" s="55" t="inlineStr">
         <is>
           <t>CÓDIGO DE TITULAR PREVIO (T0000)</t>
         </is>
       </c>
-      <c r="C122" s="55" t="inlineStr">
+      <c r="C123" s="55" t="inlineStr">
         <is>
           <t>S91</t>
         </is>
       </c>
-      <c r="D122" s="55" t="inlineStr">
+      <c r="D123" s="55" t="inlineStr">
         <is>
           <t>cod_titular_prev</t>
         </is>
       </c>
-      <c r="E122" s="55" t="inlineStr">
+      <c r="E123" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="56" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="56" t="inlineStr">
         <is>
           <t>6. DISPONIBILIDAD Y CONDICIÓN DE LIBERACIÓN</t>
         </is>
       </c>
-      <c r="B123" s="56" t="inlineStr">
+      <c r="B124" s="56" t="inlineStr">
         <is>
           <t>OBSERVACIONES / ALERTAS SOCIALES</t>
         </is>
       </c>
-      <c r="C123" s="56" t="inlineStr">
+      <c r="C124" s="56" t="inlineStr">
         <is>
           <t>G92</t>
         </is>
       </c>
-      <c r="D123" s="56" t="inlineStr">
+      <c r="D124" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E123" s="56" t="inlineStr">
+      <c r="E124" s="56" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="55" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="55" t="inlineStr">
         <is>
           <t>7. CROQUIS DEL PREDIO Y PUNTOS DE CONTROL (UTM WGS84 Zona 17S)</t>
         </is>
       </c>
-      <c r="B124" s="55" t="inlineStr">
+      <c r="B125" s="55" t="inlineStr">
         <is>
           <t>Puntos de control / vértices</t>
         </is>
       </c>
-      <c r="C124" s="55" t="inlineStr">
+      <c r="C125" s="55" t="inlineStr">
         <is>
           <t>B110:Y117</t>
         </is>
       </c>
-      <c r="D124" s="55" t="inlineStr">
+      <c r="D125" s="55" t="inlineStr">
         <is>
           <t>r_puntos: pt_gps, pt_tipo</t>
         </is>
       </c>
-      <c r="E124" s="55" t="inlineStr">
+      <c r="E125" s="55" t="inlineStr">
         <is>
           <t>Tabla</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="56" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="56" t="inlineStr">
         <is>
           <t>8. PANEL FOTOGRÁFICO</t>
         </is>
       </c>
-      <c r="B125" s="56" t="inlineStr">
+      <c r="B126" s="56" t="inlineStr">
         <is>
           <t>Foto 1 – Vista general del predio</t>
         </is>
       </c>
-      <c r="C125" s="56" t="inlineStr">
+      <c r="C126" s="56" t="inlineStr">
         <is>
           <t>B120</t>
         </is>
       </c>
-      <c r="D125" s="56" t="inlineStr">
+      <c r="D126" s="56" t="inlineStr">
         <is>
           <t>foto_1</t>
         </is>
       </c>
-      <c r="E125" s="56" t="inlineStr">
+      <c r="E126" s="56" t="inlineStr">
         <is>
           <t>Imagen</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="55" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="55" t="inlineStr">
         <is>
           <t>8. PANEL FOTOGRÁFICO</t>
         </is>
       </c>
-      <c r="B126" s="55" t="inlineStr">
+      <c r="B127" s="55" t="inlineStr">
         <is>
           <t>Foto 2 – Cobertura vegetal / uso actual</t>
         </is>
       </c>
-      <c r="C126" s="55" t="inlineStr">
+      <c r="C127" s="55" t="inlineStr">
         <is>
           <t>N120</t>
         </is>
       </c>
-      <c r="D126" s="55" t="inlineStr">
+      <c r="D127" s="55" t="inlineStr">
         <is>
           <t>foto_2</t>
         </is>
       </c>
-      <c r="E126" s="55" t="inlineStr">
+      <c r="E127" s="55" t="inlineStr">
         <is>
           <t>Imagen</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="56" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="56" t="inlineStr">
         <is>
           <t>8. PANEL FOTOGRÁFICO</t>
         </is>
       </c>
-      <c r="B127" s="56" t="inlineStr">
+      <c r="B128" s="56" t="inlineStr">
         <is>
           <t>Foto 3 – Linderos, hitos o accesos</t>
         </is>
       </c>
-      <c r="C127" s="56" t="inlineStr">
+      <c r="C128" s="56" t="inlineStr">
         <is>
           <t>B135</t>
         </is>
       </c>
-      <c r="D127" s="56" t="inlineStr">
+      <c r="D128" s="56" t="inlineStr">
         <is>
           <t>foto_3</t>
         </is>
       </c>
-      <c r="E127" s="56" t="inlineStr">
+      <c r="E128" s="56" t="inlineStr">
         <is>
           <t>Imagen</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="55" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="55" t="inlineStr">
         <is>
           <t>8. PANEL FOTOGRÁFICO</t>
         </is>
       </c>
-      <c r="B128" s="55" t="inlineStr">
+      <c r="B129" s="55" t="inlineStr">
         <is>
           <t>Foto 4 – Interferencias o detalle relevante</t>
         </is>
       </c>
-      <c r="C128" s="55" t="inlineStr">
+      <c r="C129" s="55" t="inlineStr">
         <is>
           <t>N135</t>
         </is>
       </c>
-      <c r="D128" s="55" t="inlineStr">
+      <c r="D129" s="55" t="inlineStr">
         <is>
           <t>foto_4</t>
         </is>
       </c>
-      <c r="E128" s="55" t="inlineStr">
+      <c r="E129" s="55" t="inlineStr">
         <is>
           <t>Imagen</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="56" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="56" t="inlineStr">
         <is>
           <t>9. CONFORMIDAD Y FIRMAS</t>
         </is>
       </c>
-      <c r="B129" s="56" t="inlineStr">
+      <c r="B130" s="56" t="inlineStr">
         <is>
           <t>FECHA DE ELABORACIÓN</t>
         </is>
       </c>
-      <c r="C129" s="56" t="inlineStr">
+      <c r="C130" s="56" t="inlineStr">
         <is>
           <t>G160</t>
         </is>
       </c>
-      <c r="D129" s="56" t="inlineStr">
+      <c r="D130" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E129" s="56" t="inlineStr">
+      <c r="E130" s="56" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="55" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="55" t="inlineStr">
         <is>
           <t>9. CONFORMIDAD Y FIRMAS</t>
         </is>
       </c>
-      <c r="B130" s="55" t="inlineStr">
+      <c r="B131" s="55" t="inlineStr">
         <is>
           <t>LUGAR</t>
         </is>
       </c>
-      <c r="C130" s="55" t="inlineStr">
+      <c r="C131" s="55" t="inlineStr">
         <is>
           <t>S160</t>
         </is>
       </c>
-      <c r="D130" s="55" t="inlineStr">
+      <c r="D131" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E130" s="55" t="inlineStr">
+      <c r="E131" s="55" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A33:E130"/>
-  <mergeCells count="11">
+  <autoFilter ref="A34:E131"/>
+  <mergeCells count="12">
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
@@ -20196,4 +20205,2959 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C173"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>celda</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>asistente</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>unidad</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>n_predio</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G16</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fecha_insp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hoy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>consentimiento</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sit_registral</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>doc_partida</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>reg_personeria</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>G22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>oficina_registral</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>reg_titular</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>G23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>docs_exhibidos_1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>G24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>docs_exhibidos_2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>docs_exhibidos_3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tipo_titularidad</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>G27</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>personeria</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sucesion_estado</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>G28</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tit_nombres</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tit_apellidos</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tit_dni</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>G31</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tit_celular</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tit_estado_civil</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>G32</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tit_correo</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cony_nombre</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>G33</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cony_dni</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S33</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cc_nombre</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>G35</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cc_ruc</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>G36</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cc_partida</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S36</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cc_presidente</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>G37</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>rep_cargo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S37</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cc_presidente_dni</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>G38</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cc_presidente_cel</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S38</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dom_direccion</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B41</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dom_distrito</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>L41</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dom_provincia</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Q41</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dom_departamento</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>V41</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>predio_nombre</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>G44</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>centro_poblado</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>G45</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>comunidad</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S45</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ref_acceso</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>G46</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>acceso_tipo</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>G47</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>tiempo_acceso_min</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S47</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>utm_este</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>G49</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>utm_norte</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>S49</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>utm_altitud</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>G50</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>utm_precision</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>S50</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>predio_departamento</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>G51</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>predio_provincia</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>S51</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>predio_distrito</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>G52</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>uso_actual</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>G55</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>uso_otro</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>S55</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ocupacion</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>G56</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ocupacion_det</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>S56</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>edificaciones</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>G57</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>edif_det</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>pendiente_clase</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>G58</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>erosion</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>S58</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cobertura</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>G59</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>mov_masa</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>descripcion_predio</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>G60</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>tipo_predio</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>G62</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>predio_area_decl_ha</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>S62</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>perimetro_m</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>G63</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>col_norte</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>F66</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>col_norte_tipo</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>S66</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>col_este</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>F67</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>col_este_tipo</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>S67</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>col_sur</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>F68</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>col_sur_tipo</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>S68</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>col_oeste</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>F69</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>col_oeste_tipo</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>S69</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>conflicto_linderos_det</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>G70</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>predio_area_unidad_ha</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>G74</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>interferencias_1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>G77</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>interferencias_2</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>M77</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>interferencias_3</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>S77</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>interf_detalle</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>G78</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>intervencion_prevista_1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>G79</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>intervencion_prevista_2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P79</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>af_descripcion_1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D82</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>af_metrado_1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>I82</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>af_und_1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>K82</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>af_material_1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>M82</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>af_conservacion_1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P82</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>af_construccion_1</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>S82</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>af_ubicacion_1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>V82</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>af_descripcion_2</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D83</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>af_metrado_2</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>I83</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>af_und_2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>K83</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>af_material_2</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>M83</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>af_conservacion_2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>P83</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>af_construccion_2</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>S83</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>af_ubicacion_2</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>V83</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>af_descripcion_3</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>af_metrado_3</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>I84</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>af_und_3</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>K84</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>af_material_3</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>M84</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>af_conservacion_3</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>P84</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>af_construccion_3</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>S84</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>af_ubicacion_3</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>V84</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>af_descripcion_4</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D85</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>af_metrado_4</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>I85</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>af_und_4</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>K85</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>af_material_4</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>M85</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>af_conservacion_4</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>P85</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>af_construccion_4</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>S85</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>af_ubicacion_4</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>V85</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>af_descripcion_5</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D86</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>af_metrado_5</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>I86</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>af_und_5</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>K86</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>af_material_5</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>M86</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>af_conservacion_5</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>P86</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>af_construccion_5</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>S86</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>af_ubicacion_5</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>V86</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>aceptacion</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>G89</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>modalidad</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>S89</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>conclusion_campo</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>G90</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>estado_la_propuesto</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>S90</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>tipo_acta_prevista</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>G91</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cod_titular_prev</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>S91</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>alertas</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>G92</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>croquis</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>B95</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>pt_tipo_1</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>pt_este_1</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>I110</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>pt_norte_1</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>N110</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>pt_alt_1</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>S110</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>pt_obs_1</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>V110</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>pt_tipo_2</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D111</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>pt_este_2</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>I111</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>pt_norte_2</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>N111</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>pt_alt_2</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>S111</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>pt_obs_2</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>V111</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>pt_tipo_3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>pt_este_3</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>I112</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>pt_norte_3</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>N112</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>pt_alt_3</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>S112</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>pt_obs_3</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>V112</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>pt_tipo_4</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>pt_este_4</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>I113</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>pt_norte_4</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>N113</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>pt_alt_4</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>S113</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>pt_obs_4</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>V113</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>pt_tipo_5</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>pt_este_5</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>I114</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>pt_norte_5</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>N114</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>pt_alt_5</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>S114</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>pt_obs_5</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>V114</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>pt_tipo_6</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>pt_este_6</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>I115</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>pt_norte_6</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>N115</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>pt_alt_6</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>S115</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>pt_obs_6</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>V115</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>pt_tipo_7</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>pt_este_7</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>I116</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>pt_norte_7</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>N116</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>pt_alt_7</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>S116</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>pt_obs_7</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>V116</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>pt_tipo_8</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D117</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>pt_este_8</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>I117</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>pt_norte_8</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>N117</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>pt_alt_8</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>S117</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>pt_obs_8</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>V117</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>foto_1</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>B120</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>foto_1_archivo</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>F133</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>foto_2</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>N120</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>foto_2_archivo</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>R133</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>foto_3</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>B135</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>foto_3_archivo</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>F148</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>foto_4</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>N135</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>foto_4_archivo</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>R148</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>fecha_elaboracion</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>G160</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>lugar</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>S160</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>FP-2026.10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>